--- a/Nhom01/SE_9/SE_9_Nhom01_Features.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_Features.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>At least 10 features; each has ID, name, short description and exactly one parent epic.</t>
+          <t>Có ít nhất 10 tính năng; mỗi tính năng có mã, tên, mô tả ngắn và đúng một nhóm nghiệp vụ cha.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 2–27, A:E</t>
+          <t>FE-001–FE-026; EP-001–EP-005</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>A feature is one capability in its epic and groups related user stories.</t>
+          <t>Mỗi tính năng là một năng lực thuộc nhóm nghiệp vụ và là nhóm chứa các câu chuyện người dùng liên quan.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Features rows 2–27; UserStory rows 2–17; Wish List RAW-001 row 2; image (1).png, business-flow item 1 and account-provisioning statement.</t>
+          <t>FE-001–FE-026; US-001–US-016; RAW-001; Đề bài – luồng nghiệp vụ “Đăng kí tài khoản”</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
